--- a/docs/downloads/04/tbl_other_act_all_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Elève, Etudiant- Mpianatra</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +441,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -490,12 +466,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -508,12 +478,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -544,12 +508,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,12 +520,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -598,12 +550,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -634,12 +580,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +592,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +604,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +616,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +628,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +640,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -796,12 +706,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +718,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -845,12 +743,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -863,12 +755,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -881,12 +767,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -899,12 +779,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -971,12 +845,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -989,12 +857,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1007,12 +869,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1043,12 +899,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1079,12 +929,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-      <c r="D41">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1097,12 +941,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1128,12 +966,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1164,12 +996,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1182,12 +1008,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1236,12 +1056,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1254,12 +1068,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1308,12 +1116,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1326,12 +1128,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1344,12 +1140,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C56">
-        <v>3</v>
-      </c>
-      <c r="D56">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1362,12 +1152,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1380,12 +1164,6 @@
           <t>Taxi-bicyclette</t>
         </is>
       </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1411,12 +1189,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1429,12 +1201,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1447,12 +1213,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1465,12 +1225,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
-      <c r="D63">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1483,12 +1237,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1537,12 +1285,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1555,12 +1297,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1573,12 +1309,6 @@
           <t>Inactif, Chômeur ? Tsy miasa, tsy an?asa</t>
         </is>
       </c>
-      <c r="C69">
-        <v>3</v>
-      </c>
-      <c r="D69">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1640,12 +1370,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1694,12 +1418,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1712,12 +1430,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1748,12 +1460,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
-      <c r="D79">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1766,12 +1472,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1784,12 +1484,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C81">
-        <v>3</v>
-      </c>
-      <c r="D81">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1802,12 +1496,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1838,12 +1526,6 @@
           <t>Ouvrier agricole (salarié agricole) - Mpanao saraka an- tsaha</t>
         </is>
       </c>
-      <c r="C84">
-        <v>2</v>
-      </c>
-      <c r="D84">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1856,12 +1538,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1874,12 +1550,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1905,12 +1575,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1923,12 +1587,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-      <c r="D89">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1977,12 +1635,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C92">
-        <v>3</v>
-      </c>
-      <c r="D92">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2013,12 +1665,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C94">
-        <v>3</v>
-      </c>
-      <c r="D94">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2031,12 +1677,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C95">
-        <v>2</v>
-      </c>
-      <c r="D95">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2067,12 +1707,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C97">
-        <v>1</v>
-      </c>
-      <c r="D97">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2085,12 +1719,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2121,12 +1749,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2139,12 +1761,6 @@
           <t>Salarié en élevage- Mpikarama @ fiompiana</t>
         </is>
       </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="D101">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2157,12 +1773,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C102">
-        <v>2</v>
-      </c>
-      <c r="D102">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2206,12 +1816,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C105">
-        <v>1</v>
-      </c>
-      <c r="D105">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2260,12 +1864,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C108">
-        <v>1</v>
-      </c>
-      <c r="D108">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2278,12 +1876,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
-      <c r="D109">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2296,12 +1888,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2332,12 +1918,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2368,12 +1948,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C114">
-        <v>1</v>
-      </c>
-      <c r="D114">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2386,12 +1960,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C115">
-        <v>2</v>
-      </c>
-      <c r="D115">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2404,12 +1972,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C116">
-        <v>1</v>
-      </c>
-      <c r="D116">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2435,12 +1997,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-      <c r="D118">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2453,12 +2009,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C119">
-        <v>4</v>
-      </c>
-      <c r="D119">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2471,12 +2021,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C120">
-        <v>2</v>
-      </c>
-      <c r="D120">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2489,12 +2033,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-      <c r="D121">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2507,12 +2045,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C122">
-        <v>4</v>
-      </c>
-      <c r="D122">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2525,12 +2057,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C123">
-        <v>1</v>
-      </c>
-      <c r="D123">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2543,12 +2069,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C124">
-        <v>2</v>
-      </c>
-      <c r="D124">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2579,12 +2099,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C126">
-        <v>3</v>
-      </c>
-      <c r="D126">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2597,12 +2111,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C127">
-        <v>2</v>
-      </c>
-      <c r="D127">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2615,12 +2123,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C128">
-        <v>3</v>
-      </c>
-      <c r="D128">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2651,12 +2153,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C130">
-        <v>1</v>
-      </c>
-      <c r="D130">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2705,12 +2201,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C133">
-        <v>2</v>
-      </c>
-      <c r="D133">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2741,12 +2231,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C135">
-        <v>3</v>
-      </c>
-      <c r="D135">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2759,12 +2243,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C136">
-        <v>2</v>
-      </c>
-      <c r="D136">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2795,12 +2273,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C138">
-        <v>3</v>
-      </c>
-      <c r="D138">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2813,12 +2285,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C139">
-        <v>1</v>
-      </c>
-      <c r="D139">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2867,12 +2333,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C142">
-        <v>1</v>
-      </c>
-      <c r="D142">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2903,12 +2363,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C144">
-        <v>1</v>
-      </c>
-      <c r="D144">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2957,12 +2411,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-      <c r="D147">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2975,12 +2423,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C148">
-        <v>2</v>
-      </c>
-      <c r="D148">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2993,12 +2435,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C149">
-        <v>3</v>
-      </c>
-      <c r="D149">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3011,12 +2447,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C150">
-        <v>2</v>
-      </c>
-      <c r="D150">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3046,12 +2476,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C152">
-        <v>2</v>
-      </c>
-      <c r="D152">
-        <v>0.1</v>
       </c>
     </row>
     <row r="153">
